--- a/历史/大事年表.xlsx
+++ b/历史/大事年表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wpf_custom\workspace\github\my-note-2\历史\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{998830E8-A01B-42FD-A9FC-E483F8814B38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DE09F5C-1413-45D2-8F78-19A802DCFFE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="450" yWindow="405" windowWidth="22605" windowHeight="14580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="169">
   <si>
     <t>前 3000</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -839,6 +839,14 @@
   </si>
   <si>
     <t>七年战争结束，巴黎条约签订。英国大获全胜，奠定了日不落帝国的地位。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>波士顿大屠杀/国王街事件。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>波士顿倾茶事件</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1429,7 +1437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R113"/>
+  <dimension ref="A1:R115"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1563,7 +1571,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="28.5">
+    <row r="9" spans="1:18">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -2334,7 +2342,7 @@
       <c r="N69" s="14"/>
       <c r="Q69" s="15"/>
     </row>
-    <row r="70" spans="1:18" ht="42.75">
+    <row r="70" spans="1:18" ht="28.5">
       <c r="A70" s="11">
         <v>1707</v>
       </c>
@@ -2379,40 +2387,35 @@
         <v>166</v>
       </c>
     </row>
-    <row r="73" spans="1:18" ht="28.5">
+    <row r="73" spans="1:18" ht="15">
       <c r="A73" s="11">
-        <v>1775</v>
+        <v>1770</v>
       </c>
       <c r="D73" s="20"/>
       <c r="G73" s="19"/>
       <c r="H73" s="29"/>
       <c r="K73" s="13"/>
       <c r="N73" s="14"/>
-      <c r="P73" s="29"/>
-      <c r="R73" s="24" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="74" spans="1:18" ht="28.5">
+      <c r="P73" s="29" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" ht="15">
       <c r="A74" s="11">
-        <v>1776</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>88</v>
+        <v>1773</v>
       </c>
       <c r="D74" s="20"/>
       <c r="G74" s="19"/>
       <c r="H74" s="29"/>
       <c r="K74" s="13"/>
       <c r="N74" s="14"/>
-      <c r="P74" s="29"/>
-      <c r="R74" s="24" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="75" spans="1:18" ht="15">
+      <c r="P74" s="29" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" ht="28.5">
       <c r="A75" s="11">
-        <v>1783</v>
+        <v>1775</v>
       </c>
       <c r="D75" s="20"/>
       <c r="G75" s="19"/>
@@ -2421,373 +2424,380 @@
       <c r="N75" s="14"/>
       <c r="P75" s="29"/>
       <c r="R75" s="24" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="76" spans="1:18" ht="15">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" ht="28.5">
       <c r="A76" s="11">
-        <v>1789</v>
+        <v>1776</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="D76" s="20"/>
       <c r="G76" s="19"/>
-      <c r="H76" s="29" t="s">
-        <v>89</v>
-      </c>
+      <c r="H76" s="29"/>
       <c r="K76" s="13"/>
       <c r="N76" s="14"/>
       <c r="P76" s="29"/>
-      <c r="R76" s="24"/>
-    </row>
-    <row r="77" spans="1:18" ht="28.5">
+      <c r="R76" s="24" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" ht="15">
       <c r="A77" s="11">
-        <v>1792</v>
+        <v>1783</v>
       </c>
       <c r="D77" s="20"/>
       <c r="G77" s="19"/>
-      <c r="H77" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="I77" s="30" t="s">
-        <v>146</v>
-      </c>
+      <c r="H77" s="29"/>
       <c r="K77" s="13"/>
       <c r="N77" s="14"/>
       <c r="P77" s="29"/>
-      <c r="R77" s="24"/>
-    </row>
-    <row r="78" spans="1:18" ht="28.5">
+      <c r="R77" s="24" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" ht="15">
       <c r="A78" s="11">
-        <v>1797</v>
+        <v>1789</v>
       </c>
       <c r="D78" s="20"/>
       <c r="G78" s="19"/>
-      <c r="I78" s="30"/>
-      <c r="K78" s="13" t="s">
-        <v>136</v>
-      </c>
+      <c r="H78" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="K78" s="13"/>
       <c r="N78" s="14"/>
       <c r="P78" s="29"/>
       <c r="R78" s="24"/>
     </row>
-    <row r="79" spans="1:18" ht="15">
+    <row r="79" spans="1:18" ht="28.5">
       <c r="A79" s="11">
-        <v>1800</v>
+        <v>1792</v>
       </c>
       <c r="D79" s="20"/>
       <c r="G79" s="19"/>
-      <c r="I79" s="30"/>
+      <c r="H79" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="I79" s="30" t="s">
+        <v>146</v>
+      </c>
+      <c r="K79" s="13"/>
       <c r="N79" s="14"/>
-      <c r="P79" s="29" t="s">
-        <v>155</v>
-      </c>
+      <c r="P79" s="29"/>
       <c r="R79" s="24"/>
     </row>
-    <row r="80" spans="1:18" ht="42.75">
+    <row r="80" spans="1:18" ht="28.5">
       <c r="A80" s="11">
-        <v>1801</v>
+        <v>1797</v>
       </c>
       <c r="D80" s="20"/>
       <c r="G80" s="19"/>
       <c r="I80" s="30"/>
+      <c r="K80" s="13" t="s">
+        <v>136</v>
+      </c>
       <c r="N80" s="14"/>
-      <c r="P80" s="14" t="s">
-        <v>156</v>
-      </c>
+      <c r="P80" s="29"/>
       <c r="R80" s="24"/>
     </row>
-    <row r="81" spans="1:18" ht="28.5">
+    <row r="81" spans="1:18" ht="15">
       <c r="A81" s="11">
-        <v>1804</v>
+        <v>1800</v>
       </c>
       <c r="D81" s="20"/>
       <c r="G81" s="19"/>
-      <c r="H81" s="25" t="s">
+      <c r="I81" s="30"/>
+      <c r="N81" s="14"/>
+      <c r="P81" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="R81" s="24"/>
+    </row>
+    <row r="82" spans="1:18" ht="28.5">
+      <c r="A82" s="11">
+        <v>1801</v>
+      </c>
+      <c r="D82" s="20"/>
+      <c r="G82" s="19"/>
+      <c r="I82" s="30"/>
+      <c r="N82" s="14"/>
+      <c r="P82" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="R82" s="24"/>
+    </row>
+    <row r="83" spans="1:18" ht="28.5">
+      <c r="A83" s="11">
+        <v>1804</v>
+      </c>
+      <c r="D83" s="20"/>
+      <c r="G83" s="19"/>
+      <c r="H83" s="25" t="s">
         <v>144</v>
       </c>
-      <c r="I81" s="30" t="s">
+      <c r="I83" s="30" t="s">
         <v>147</v>
       </c>
-      <c r="N81" s="14"/>
-      <c r="P81" s="14"/>
-      <c r="R81" s="24"/>
-    </row>
-    <row r="82" spans="1:18" ht="57">
-      <c r="A82" s="11">
-        <v>1806</v>
-      </c>
-      <c r="D82" s="20"/>
-      <c r="G82" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="H82" s="25"/>
-      <c r="N82" s="14"/>
-      <c r="P82" s="14"/>
-      <c r="R82" s="24"/>
-    </row>
-    <row r="83" spans="1:18" ht="15">
-      <c r="A83" s="11">
-        <v>1811</v>
-      </c>
-      <c r="B83" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D83" s="20"/>
-      <c r="H83" s="25"/>
       <c r="N83" s="14"/>
       <c r="P83" s="14"/>
       <c r="R83" s="24"/>
     </row>
-    <row r="84" spans="1:18" ht="28.5">
+    <row r="84" spans="1:18" ht="57">
       <c r="A84" s="11">
-        <v>1815</v>
+        <v>1806</v>
       </c>
       <c r="D84" s="20"/>
-      <c r="H84" s="25" t="s">
-        <v>91</v>
-      </c>
+      <c r="G84" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="H84" s="25"/>
       <c r="N84" s="14"/>
       <c r="P84" s="14"/>
       <c r="R84" s="24"/>
     </row>
     <row r="85" spans="1:18" ht="15">
       <c r="A85" s="11">
-        <v>1840</v>
-      </c>
-      <c r="D85" s="20" t="s">
-        <v>92</v>
-      </c>
+        <v>1811</v>
+      </c>
+      <c r="B85" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D85" s="20"/>
+      <c r="H85" s="25"/>
       <c r="N85" s="14"/>
       <c r="P85" s="14"/>
       <c r="R85" s="24"/>
     </row>
     <row r="86" spans="1:18" ht="28.5">
       <c r="A86" s="11">
-        <v>1848</v>
+        <v>1815</v>
       </c>
       <c r="D86" s="20"/>
+      <c r="H86" s="25" t="s">
+        <v>91</v>
+      </c>
       <c r="N86" s="14"/>
       <c r="P86" s="14"/>
-      <c r="R86" s="24" t="s">
-        <v>165</v>
-      </c>
+      <c r="R86" s="24"/>
     </row>
     <row r="87" spans="1:18" ht="15">
       <c r="A87" s="11">
-        <v>1858</v>
-      </c>
-      <c r="D87" s="20"/>
-      <c r="F87" s="11" t="s">
-        <v>93</v>
+        <v>1840</v>
+      </c>
+      <c r="D87" s="20" t="s">
+        <v>92</v>
       </c>
       <c r="N87" s="14"/>
       <c r="P87" s="14"/>
       <c r="R87" s="24"/>
     </row>
-    <row r="88" spans="1:18" ht="15">
+    <row r="88" spans="1:18" ht="28.5">
       <c r="A88" s="11">
-        <v>1860</v>
-      </c>
-      <c r="D88" s="20" t="s">
-        <v>94</v>
-      </c>
+        <v>1848</v>
+      </c>
+      <c r="D88" s="20"/>
       <c r="N88" s="14"/>
       <c r="P88" s="14"/>
-      <c r="R88" s="24"/>
+      <c r="R88" s="24" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="89" spans="1:18" ht="15">
       <c r="A89" s="11">
-        <v>1861</v>
+        <v>1858</v>
       </c>
       <c r="D89" s="20"/>
+      <c r="F89" s="11" t="s">
+        <v>93</v>
+      </c>
       <c r="N89" s="14"/>
       <c r="P89" s="14"/>
-      <c r="R89" s="24" t="s">
-        <v>148</v>
-      </c>
+      <c r="R89" s="24"/>
     </row>
     <row r="90" spans="1:18" ht="15">
       <c r="A90" s="11">
-        <v>1865</v>
-      </c>
-      <c r="D90" s="20"/>
+        <v>1860</v>
+      </c>
+      <c r="D90" s="20" t="s">
+        <v>94</v>
+      </c>
       <c r="N90" s="14"/>
       <c r="P90" s="14"/>
-      <c r="R90" s="24" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="91" spans="1:18" ht="30">
+      <c r="R90" s="24"/>
+    </row>
+    <row r="91" spans="1:18" ht="15">
       <c r="A91" s="11">
-        <v>1866</v>
-      </c>
-      <c r="B91" s="11" t="s">
-        <v>95</v>
+        <v>1861</v>
       </c>
       <c r="D91" s="20"/>
       <c r="N91" s="14"/>
       <c r="P91" s="14"/>
-      <c r="R91" s="24"/>
+      <c r="R91" s="24" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="92" spans="1:18" ht="15">
       <c r="A92" s="11">
-        <v>1867</v>
-      </c>
-      <c r="B92" s="11" t="s">
-        <v>96</v>
+        <v>1865</v>
       </c>
       <c r="D92" s="20"/>
       <c r="N92" s="14"/>
       <c r="P92" s="14"/>
-      <c r="R92" s="24"/>
-    </row>
-    <row r="93" spans="1:18" ht="45">
+      <c r="R92" s="24" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" ht="30">
       <c r="A93" s="11">
-        <v>1886</v>
+        <v>1866</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D93" s="20"/>
       <c r="N93" s="14"/>
       <c r="P93" s="14"/>
       <c r="R93" s="24"/>
     </row>
-    <row r="94" spans="1:18" ht="28.5">
+    <row r="94" spans="1:18" ht="15">
       <c r="A94" s="11">
-        <v>1879</v>
+        <v>1867</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="D94" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="E94" s="13" t="s">
-        <v>101</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="D94" s="20"/>
       <c r="N94" s="14"/>
       <c r="P94" s="14"/>
       <c r="R94" s="24"/>
     </row>
-    <row r="95" spans="1:18" ht="15">
+    <row r="95" spans="1:18" ht="45">
       <c r="A95" s="11">
-        <v>1914</v>
+        <v>1886</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="E95" s="13"/>
+        <v>97</v>
+      </c>
+      <c r="D95" s="20"/>
       <c r="N95" s="14"/>
       <c r="P95" s="14"/>
       <c r="R95" s="24"/>
     </row>
-    <row r="96" spans="1:18" ht="66">
+    <row r="96" spans="1:18" ht="28.5">
       <c r="A96" s="11">
-        <v>1917</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="E96" s="13"/>
+        <v>1879</v>
+      </c>
+      <c r="B96" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="D96" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="E96" s="13" t="s">
+        <v>101</v>
+      </c>
       <c r="N96" s="14"/>
       <c r="P96" s="14"/>
       <c r="R96" s="24"/>
     </row>
     <row r="97" spans="1:18" ht="15">
       <c r="A97" s="11">
-        <v>1918</v>
+        <v>1914</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E97" s="13"/>
       <c r="N97" s="14"/>
       <c r="P97" s="14"/>
       <c r="R97" s="24"/>
     </row>
-    <row r="98" spans="1:18" ht="15">
+    <row r="98" spans="1:18" ht="66">
       <c r="A98" s="11">
-        <v>1921</v>
-      </c>
-      <c r="D98" s="26" t="s">
-        <v>106</v>
+        <v>1917</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>104</v>
       </c>
       <c r="E98" s="13"/>
       <c r="N98" s="14"/>
       <c r="P98" s="14"/>
       <c r="R98" s="24"/>
     </row>
-    <row r="99" spans="1:18" ht="30">
+    <row r="99" spans="1:18" ht="15">
       <c r="A99" s="11">
-        <v>1922</v>
+        <v>1918</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="D99" s="26"/>
+        <v>105</v>
+      </c>
       <c r="E99" s="13"/>
-      <c r="N99" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="P99" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q99" s="26" t="s">
-        <v>160</v>
-      </c>
+      <c r="N99" s="14"/>
+      <c r="P99" s="14"/>
       <c r="R99" s="24"/>
     </row>
     <row r="100" spans="1:18" ht="15">
       <c r="A100" s="11">
+        <v>1921</v>
+      </c>
+      <c r="D100" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="E100" s="13"/>
+      <c r="N100" s="14"/>
+      <c r="P100" s="14"/>
+      <c r="R100" s="24"/>
+    </row>
+    <row r="101" spans="1:18" ht="30">
+      <c r="A101" s="11">
+        <v>1922</v>
+      </c>
+      <c r="B101" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="D101" s="26"/>
+      <c r="E101" s="13"/>
+      <c r="N101" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="P101" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q101" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="R101" s="24"/>
+    </row>
+    <row r="102" spans="1:18" ht="15">
+      <c r="A102" s="11">
         <v>1927</v>
       </c>
-      <c r="B100" s="11"/>
-      <c r="D100" s="26"/>
-      <c r="E100" s="13"/>
-      <c r="Q100" s="26"/>
-      <c r="R100" s="24"/>
-    </row>
-    <row r="101" spans="1:18" ht="30.75">
-      <c r="A101" s="11">
-        <v>1937</v>
-      </c>
-      <c r="D101" s="26"/>
-      <c r="E101" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q101" s="26"/>
-      <c r="R101" s="24"/>
-    </row>
-    <row r="102" spans="1:18" ht="33">
-      <c r="A102" s="11">
-        <v>1939</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>109</v>
-      </c>
+      <c r="B102" s="11"/>
       <c r="D102" s="26"/>
       <c r="E102" s="13"/>
       <c r="Q102" s="26"/>
       <c r="R102" s="24"/>
     </row>
-    <row r="103" spans="1:18" ht="15">
+    <row r="103" spans="1:18" ht="30.75">
       <c r="A103" s="11">
-        <v>1940</v>
-      </c>
-      <c r="B103" s="11" t="s">
-        <v>110</v>
+        <v>1937</v>
       </c>
       <c r="D103" s="26"/>
-      <c r="E103" s="13"/>
+      <c r="E103" s="13" t="s">
+        <v>108</v>
+      </c>
       <c r="Q103" s="26"/>
       <c r="R103" s="24"/>
     </row>
-    <row r="104" spans="1:18" ht="30.75">
+    <row r="104" spans="1:18" ht="33">
       <c r="A104" s="11">
-        <v>1941</v>
-      </c>
-      <c r="B104" s="4" t="s">
-        <v>111</v>
+        <v>1939</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>109</v>
       </c>
       <c r="D104" s="26"/>
       <c r="E104" s="13"/>
@@ -2796,10 +2806,10 @@
     </row>
     <row r="105" spans="1:18" ht="15">
       <c r="A105" s="11">
-        <v>1943</v>
+        <v>1940</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D105" s="26"/>
       <c r="E105" s="13"/>
@@ -2808,88 +2818,112 @@
     </row>
     <row r="106" spans="1:18" ht="30.75">
       <c r="A106" s="11">
-        <v>1945</v>
+        <v>1941</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D106" s="26"/>
-      <c r="E106" s="13" t="s">
-        <v>114</v>
-      </c>
+      <c r="E106" s="13"/>
       <c r="Q106" s="26"/>
       <c r="R106" s="24"/>
     </row>
-    <row r="107" spans="1:18" ht="58.5" customHeight="1">
+    <row r="107" spans="1:18" ht="15">
       <c r="A107" s="11">
-        <v>1949</v>
-      </c>
-      <c r="D107" s="5" t="s">
-        <v>115</v>
-      </c>
+        <v>1943</v>
+      </c>
+      <c r="B107" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="D107" s="26"/>
+      <c r="E107" s="13"/>
       <c r="Q107" s="26"/>
       <c r="R107" s="24"/>
     </row>
-    <row r="108" spans="1:18" ht="15">
+    <row r="108" spans="1:18" ht="30.75">
       <c r="A108" s="11">
-        <v>1966</v>
-      </c>
-      <c r="D108" s="31" t="s">
-        <v>117</v>
+        <v>1945</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D108" s="26"/>
+      <c r="E108" s="13" t="s">
+        <v>114</v>
       </c>
       <c r="Q108" s="26"/>
       <c r="R108" s="24"/>
     </row>
-    <row r="109" spans="1:18" ht="74.25">
+    <row r="109" spans="1:18" ht="58.5" customHeight="1">
       <c r="A109" s="11">
-        <v>1976</v>
+        <v>1949</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q109" s="26"/>
       <c r="R109" s="24"/>
     </row>
-    <row r="110" spans="1:18" ht="58.5" customHeight="1">
+    <row r="110" spans="1:18" ht="15">
       <c r="A110" s="11">
-        <v>1986</v>
-      </c>
-      <c r="D110" s="6" t="s">
-        <v>118</v>
+        <v>1966</v>
+      </c>
+      <c r="D110" s="31" t="s">
+        <v>117</v>
       </c>
       <c r="Q110" s="26"/>
       <c r="R110" s="24"/>
     </row>
-    <row r="111" spans="1:18" ht="15">
+    <row r="111" spans="1:18" ht="74.25">
       <c r="A111" s="11">
-        <v>1989</v>
-      </c>
-      <c r="D111" s="6" t="s">
-        <v>121</v>
+        <v>1976</v>
+      </c>
+      <c r="D111" s="5" t="s">
+        <v>116</v>
       </c>
       <c r="Q111" s="26"/>
       <c r="R111" s="24"/>
     </row>
-    <row r="112" spans="1:18" ht="30">
+    <row r="112" spans="1:18" ht="58.5" customHeight="1">
       <c r="A112" s="11">
-        <v>1991</v>
-      </c>
-      <c r="B112" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="D112" s="6"/>
+        <v>1986</v>
+      </c>
+      <c r="D112" s="6" t="s">
+        <v>118</v>
+      </c>
       <c r="Q112" s="26"/>
       <c r="R112" s="24"/>
     </row>
-    <row r="113" spans="1:18" ht="28.5">
+    <row r="113" spans="1:18" ht="15">
       <c r="A113" s="11">
-        <v>2023</v>
+        <v>1989</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q113" s="26"/>
       <c r="R113" s="24"/>
+    </row>
+    <row r="114" spans="1:18" ht="30">
+      <c r="A114" s="11">
+        <v>1991</v>
+      </c>
+      <c r="B114" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="D114" s="6"/>
+      <c r="Q114" s="26"/>
+      <c r="R114" s="24"/>
+    </row>
+    <row r="115" spans="1:18" ht="28.5">
+      <c r="A115" s="11">
+        <v>2023</v>
+      </c>
+      <c r="D115" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q115" s="26"/>
+      <c r="R115" s="24"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
